--- a/dataset_t6_grouped/results2/G4/G4_T3269_W0023F0003T0006Z000C1N93_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T3269_W0023F0003T0006Z000C1N93_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>29.63545315558905</v>
+        <v>4.815761137783221</v>
       </c>
       <c r="D2" t="n">
-        <v>27.09236344038841</v>
+        <v>4.402509059063117</v>
       </c>
       <c r="E2" t="n">
-        <v>9.413668235305991</v>
+        <v>1.529721088237223</v>
       </c>
       <c r="F2" t="n">
-        <v>8.446941622685239</v>
+        <v>1.372628013686351</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>19.19844073160968</v>
+        <v>3.119746618886572</v>
       </c>
       <c r="D3" t="n">
-        <v>16.69485419754712</v>
+        <v>2.712913807101407</v>
       </c>
       <c r="E3" t="n">
-        <v>9.413668235305991</v>
+        <v>1.529721088237223</v>
       </c>
       <c r="F3" t="n">
-        <v>8.446941622685239</v>
+        <v>1.372628013686351</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>32.7209277956755</v>
+        <v>5.317150766797269</v>
       </c>
       <c r="D4" t="n">
-        <v>31.57947850548747</v>
+        <v>5.131665257141713</v>
       </c>
       <c r="E4" t="n">
-        <v>9.413668235305991</v>
+        <v>1.529721088237223</v>
       </c>
       <c r="F4" t="n">
-        <v>8.446941622685239</v>
+        <v>1.372628013686351</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>34.11601673127143</v>
+        <v>5.543852718831608</v>
       </c>
       <c r="D5" t="n">
-        <v>14.80709289496085</v>
+        <v>2.406152595431138</v>
       </c>
       <c r="E5" t="n">
-        <v>9.413668235305991</v>
+        <v>1.529721088237223</v>
       </c>
       <c r="F5" t="n">
-        <v>8.446941622685239</v>
+        <v>1.372628013686351</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>25.55049517351807</v>
+        <v>4.151955465696687</v>
       </c>
       <c r="D6" t="n">
-        <v>26.69923209132653</v>
+        <v>4.338625214840562</v>
       </c>
       <c r="E6" t="n">
-        <v>9.413668235305991</v>
+        <v>1.529721088237223</v>
       </c>
       <c r="F6" t="n">
-        <v>8.446941622685239</v>
+        <v>1.372628013686351</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>12.98119289707712</v>
+        <v>2.109443845775033</v>
       </c>
       <c r="D7" t="n">
-        <v>11.97847975221298</v>
+        <v>1.94650295973461</v>
       </c>
       <c r="E7" t="n">
-        <v>9.413668235305991</v>
+        <v>1.529721088237223</v>
       </c>
       <c r="F7" t="n">
-        <v>8.446941622685239</v>
+        <v>1.372628013686351</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>8.222006379098501</v>
+        <v>1.336076036603506</v>
       </c>
       <c r="D8" t="n">
-        <v>10.59783919179672</v>
+        <v>1.722148868666967</v>
       </c>
       <c r="E8" t="n">
-        <v>9.413668235305991</v>
+        <v>1.529721088237223</v>
       </c>
       <c r="F8" t="n">
-        <v>8.446941622685239</v>
+        <v>1.372628013686351</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>28.11538999530217</v>
+        <v>4.568750874236604</v>
       </c>
       <c r="D9" t="n">
-        <v>28.60928285244126</v>
+        <v>4.649008463521706</v>
       </c>
       <c r="E9" t="n">
-        <v>9.413668235305991</v>
+        <v>1.529721088237223</v>
       </c>
       <c r="F9" t="n">
-        <v>8.446941622685239</v>
+        <v>1.372628013686351</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>16.38357892848692</v>
+        <v>2.662331575879124</v>
       </c>
       <c r="D10" t="n">
-        <v>17.57688095201621</v>
+        <v>2.856243154702634</v>
       </c>
       <c r="E10" t="n">
-        <v>9.413668235305991</v>
+        <v>1.529721088237223</v>
       </c>
       <c r="F10" t="n">
-        <v>8.446941622685239</v>
+        <v>1.372628013686351</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>5.261515697809687</v>
+        <v>0.8549963008940741</v>
       </c>
       <c r="D11" t="n">
-        <v>5.291199918435712</v>
+        <v>0.8598199867458033</v>
       </c>
       <c r="E11" t="n">
-        <v>9.413668235305991</v>
+        <v>1.529721088237223</v>
       </c>
       <c r="F11" t="n">
-        <v>8.446941622685239</v>
+        <v>1.372628013686351</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>30.86923870422124</v>
+        <v>5.016251289435952</v>
       </c>
       <c r="D12" t="n">
-        <v>29.02151228434399</v>
+        <v>4.715995746205898</v>
       </c>
       <c r="E12" t="n">
-        <v>9.413668235305991</v>
+        <v>1.529721088237223</v>
       </c>
       <c r="F12" t="n">
-        <v>8.446941622685239</v>
+        <v>1.372628013686351</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>28.94400146947862</v>
+        <v>4.703400238790277</v>
       </c>
       <c r="D13" t="n">
-        <v>27.25475384800958</v>
+        <v>4.428897500301557</v>
       </c>
       <c r="E13" t="n">
-        <v>9.413668235305991</v>
+        <v>1.529721088237223</v>
       </c>
       <c r="F13" t="n">
-        <v>8.446941622685239</v>
+        <v>1.372628013686351</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>32.34261647447249</v>
+        <v>5.25567517710178</v>
       </c>
       <c r="D14" t="n">
-        <v>29.97736350891035</v>
+        <v>4.871321570197932</v>
       </c>
       <c r="E14" t="n">
-        <v>9.413668235305991</v>
+        <v>1.529721088237223</v>
       </c>
       <c r="F14" t="n">
-        <v>8.446941622685239</v>
+        <v>1.372628013686351</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>32.20919365667121</v>
+        <v>5.233993969209072</v>
       </c>
       <c r="D15" t="n">
-        <v>30.11541508646524</v>
+        <v>4.893754951550602</v>
       </c>
       <c r="E15" t="n">
-        <v>9.413668235305991</v>
+        <v>1.529721088237223</v>
       </c>
       <c r="F15" t="n">
-        <v>8.446941622685239</v>
+        <v>1.372628013686351</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
